--- a/artfynd/A 29032-2023 artfynd.xlsx
+++ b/artfynd/A 29032-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29032-2023 artfynd.xlsx
+++ b/artfynd/A 29032-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,127 +948,6 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av groddjur</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>73446206</v>
-      </c>
-      <c r="B4" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>208250</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Åkergroda</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Rana arvalis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tjärn O Holmeja, Sk</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>391574.9394078392</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6157304.837298037</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Svedala</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Hyby</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2017-04-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2017-04-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Skogstjärn med vitmossa</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Kristian Nilsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Per Nyström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
         <is>
           <t>Biogeografisk uppföljning av groddjur</t>
         </is>

--- a/artfynd/A 29032-2023 artfynd.xlsx
+++ b/artfynd/A 29032-2023 artfynd.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lars-Ove Jönsson, Christina Persson</t>
+          <t>Christina Persson, Lars-Ove Jönsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 29032-2023 artfynd.xlsx
+++ b/artfynd/A 29032-2023 artfynd.xlsx
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Persson, Lars-Ove Jönsson</t>
+          <t>Lars-Ove Jönsson, Christina Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 29032-2023 artfynd.xlsx
+++ b/artfynd/A 29032-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57995427</v>
+        <v>92691097</v>
       </c>
       <c r="B2" t="n">
-        <v>57575</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1766)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,31 +708,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>sträckande N</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärn O Holmeja, Sk</t>
+          <t>Holmejaskogen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>391574.9533984367</v>
+        <v>391759</v>
       </c>
       <c r="R2" t="n">
-        <v>6157305.402743241</v>
+        <v>6157071</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-04-03</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-04-03</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,31 +786,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Sandsten</t>
+          <t>Erik Hirschfeld</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Sandsten</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Kampanj Grodans år</t>
-        </is>
-      </c>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73399654</v>
+        <v>92691095</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,16 +809,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -845,42 +828,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjärn O Holmeja, Sk</t>
+          <t>Holmejaskogen, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>391574.9394078392</v>
+        <v>391759</v>
       </c>
       <c r="R3" t="n">
-        <v>6157304.837298037</v>
+        <v>6157071</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,27 +875,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-04-19</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-04-19</t>
+          <t>2021-04-24</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Skogstjärn med vitmossa</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,31 +905,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Nilsson</t>
+          <t>Erik Hirschfeld</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Nyström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av groddjur</t>
-        </is>
-      </c>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124467651</v>
+        <v>107083901</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -994,26 +951,26 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmeja skogsdunge, Eksholmssjön, Sk</t>
+          <t>Holmejaskogen, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>391711</v>
+        <v>391759</v>
       </c>
       <c r="R4" t="n">
-        <v>6157159</v>
+        <v>6157071</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1037,22 +994,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>(55.5500417, 13.2761685)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,15 +1029,1426 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107083903</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>107083900</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57258</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100065</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trana</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Grus grus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>106049875</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>107083904</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124467651</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58238</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holmeja skogsdunge, Eksholmssjön, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>391711</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6157159</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Lars-Ove Jönsson</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Lars-Ove Jönsson, Christina Persson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>92691102</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>92691099</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-04-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>106049888</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106049892</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Holmejaskogen, Sk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>391759</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6157071</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-01-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erik Hirschfeld</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>73399654</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tjärn O Holmeja, Sk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>391575</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6157305</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Skogstjärn med vitmossa</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Nilsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Nyström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av groddjur</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>57995427</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tjärn O Holmeja, Sk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>391575</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6157305</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2016-04-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2016-04-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Sandsten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Sandsten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kampanj Grodans år</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>80002161</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kolahygget/Bökebergsslätt, Sk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>391672</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6157106</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Svedala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hyby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-09-08</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-09-08</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bettina Ekdahl, Alexander Nordström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29032-2023 artfynd.xlsx
+++ b/artfynd/A 29032-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Biogeografisk uppföljning av groddjur</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73399654</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kampanj Grodans år</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57995427</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691097</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691095</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1288,6 +1313,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083901</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1403,6 +1433,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083903</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1522,6 +1557,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083900</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1637,6 +1677,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106049875</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1752,6 +1797,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107083904</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1871,6 +1921,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467651</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1990,6 +2045,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691102</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2109,6 +2169,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92691099</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2224,6 +2289,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106049888</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2339,6 +2409,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106049892</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2449,8 +2524,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80002161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>